--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.97322</v>
+        <v>16.7712</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82108</v>
+        <v>16.2417</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56902</v>
+        <v>16.73313</v>
       </c>
       <c r="F2" t="n">
-        <v>42.13006</v>
+        <v>41.25171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04987</v>
+        <v>0.05104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81097</v>
+        <v>1.80031</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67399</v>
+        <v>16.83996</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31564</v>
+        <v>16.47622</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55164</v>
+        <v>16.60876</v>
       </c>
       <c r="F3" t="n">
-        <v>42.78261</v>
+        <v>42.30839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04874</v>
+        <v>0.05083</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81652</v>
+        <v>1.82681</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72476</v>
+        <v>16.5053</v>
       </c>
       <c r="D4" t="n">
-        <v>16.19363</v>
+        <v>16.44112</v>
       </c>
       <c r="E4" t="n">
-        <v>16.28875</v>
+        <v>16.47464</v>
       </c>
       <c r="F4" t="n">
-        <v>41.79928</v>
+        <v>43.13035</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007</v>
+        <v>0.05065</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8217</v>
+        <v>1.79324</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.7225</v>
+        <v>16.87097</v>
       </c>
       <c r="D6" t="n">
-        <v>16.14737</v>
+        <v>16.20568</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55516</v>
+        <v>16.26777</v>
       </c>
       <c r="F6" t="n">
-        <v>21.79344</v>
+        <v>21.56658</v>
       </c>
       <c r="G6" t="n">
-        <v>34.19934</v>
+        <v>33.71262</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75008</v>
+        <v>16.6006</v>
       </c>
       <c r="D7" t="n">
-        <v>16.06501</v>
+        <v>15.87042</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30772</v>
+        <v>16.11667</v>
       </c>
       <c r="F7" t="n">
-        <v>21.43314</v>
+        <v>21.56728</v>
       </c>
       <c r="G7" t="n">
-        <v>34.32388</v>
+        <v>34.42982</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.56097</v>
+        <v>16.32176</v>
       </c>
       <c r="D8" t="n">
-        <v>15.95669</v>
+        <v>15.94505</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51807</v>
+        <v>16.08495</v>
       </c>
       <c r="F8" t="n">
-        <v>21.48761</v>
+        <v>21.22946</v>
       </c>
       <c r="G8" t="n">
-        <v>33.53078</v>
+        <v>33.36725</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.59439</v>
+        <v>0.59713</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10897</v>
+        <v>1.1015</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59717</v>
+        <v>0.60723</v>
       </c>
       <c r="D11" t="n">
-        <v>1.09553</v>
+        <v>1.11483</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59699</v>
+        <v>0.61319</v>
       </c>
       <c r="D12" t="n">
-        <v>1.08699</v>
+        <v>1.12412</v>
       </c>
     </row>
   </sheetData>
